--- a/hardware/kicad/fab/magpanel-carrier-robotistan-bom.xlsx
+++ b/hardware/kicad/fab/magpanel-carrier-robotistan-bom.xlsx
@@ -316,7 +316,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">R2,R3,R4,R5,R6</t>
+          <t xml:space="preserve">R2,R3,R4,R5,R6,R7</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -335,18 +335,18 @@
         </is>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">100k 1% SMD Resistor</t>
+          <t xml:space="preserve">33R 1% SMD Resistor</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">R7</t>
+          <t xml:space="preserve">R10,R11,R12,R13,R14,R15,R16,R17,R18,R19,R20,R21,R22,R23,R24,R25</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -356,45 +356,15 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">C17407</t>
+          <t xml:space="preserve">C17634</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805W8F1003T5E</t>
+          <t xml:space="preserve">0805W8F330JT5E</t>
         </is>
       </c>
       <c r="F9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33R 1% SMD Resistor</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R10,R11,R12,R13,R14,R15,R16,R17,R18,R19,R20,R21,R22,R23,R24,R25</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0805</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C17634</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0805W8F330JT5E</t>
-        </is>
-      </c>
-      <c r="F10" s="1">
         <v>16</v>
       </c>
     </row>
